--- a/public/docs/附件2.《中燃集团客服条口红黄线考核细则》.xlsx
+++ b/public/docs/附件2.《中燃集团客服条口红黄线考核细则》.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12200" tabRatio="682"/>
+    <workbookView windowWidth="30720" windowHeight="13380" tabRatio="682"/>
   </bookViews>
   <sheets>
     <sheet name="客服条口红黄线考核细则" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">客服条口红黄线考核细则!$A$3:$H$23</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">客服条口红黄线考核细则!$1:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">客服条口红黄线考核细则!$A$2:$H$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">客服条口红黄线考核细则!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
   <si>
     <t>序号</t>
   </si>
@@ -51,21 +51,6 @@
     <t>处罚标准</t>
   </si>
   <si>
-    <t>项目公司</t>
-  </si>
-  <si>
-    <t>经管集团</t>
-  </si>
-  <si>
-    <t>区域</t>
-  </si>
-  <si>
-    <t>分管领导</t>
-  </si>
-  <si>
-    <t>客服总监</t>
-  </si>
-  <si>
     <t>红线</t>
   </si>
   <si>
@@ -73,6 +58,15 @@
   </si>
   <si>
     <t>参照《中燃集团安全事故管理制度》考核标准执行</t>
+  </si>
+  <si>
+    <t>项目公司-分管领导</t>
+  </si>
+  <si>
+    <t>经管集团-分管领导</t>
+  </si>
+  <si>
+    <t>区域-客服总监</t>
   </si>
   <si>
     <t>年度安检到位率低于100%</t>
@@ -295,7 +289,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,12 +314,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Microsoft YaHei Light"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -470,7 +458,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -479,12 +467,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -670,7 +652,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -688,43 +670,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -846,52 +791,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -906,112 +854,97 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1333,17 +1266,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="11.4166666666667" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="11.4166666666667" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.46666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.23333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="56.8583333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.0166666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.3833333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1833333333333" style="1" customWidth="1"/>
+    <col min="1" max="2" width="4.77777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5555555555556" style="1" customWidth="1"/>
+    <col min="4" max="4" width="95.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="40.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6666666666667" style="1" customWidth="1"/>
     <col min="9" max="16384" width="11.4166666666667" style="1"/>
   </cols>
   <sheetData>
@@ -1363,555 +1294,557 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:8">
+      <c r="A2" s="4">
+        <f>ROW()-3</f>
+        <v>-1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:8">
+      <c r="A3" s="4">
+        <f t="shared" ref="A3:A12" si="0">ROW()-3</f>
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" ht="29" customHeight="1" spans="1:8">
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:8">
       <c r="A4" s="4">
-        <f>ROW()-3</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" ht="136" customHeight="1" spans="1:8">
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:8">
       <c r="A5" s="4">
-        <f t="shared" ref="A5:A14" si="0">ROW()-3</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1" spans="1:8">
+      <c r="H5" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:8">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="88" customHeight="1" spans="1:8">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:8">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" ht="81" customHeight="1" spans="1:8">
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:8">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="72.5" spans="1:8">
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:8">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="1:8">
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:8">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" ht="43" customHeight="1" spans="1:8">
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:8">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" ht="39" customHeight="1" spans="1:8">
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:8">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" ht="31" customHeight="1" spans="1:8">
+      <c r="B12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:8">
       <c r="A13" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A13:A21" si="1">ROW()-3</f>
         <v>10</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" ht="130" customHeight="1" spans="1:8">
+      <c r="C13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1" spans="1:8">
+      <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:8">
       <c r="A15" s="4">
-        <f t="shared" ref="A15:A23" si="1">ROW()-3</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" ht="74" customHeight="1" spans="1:8">
+      <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:8">
       <c r="A16" s="4">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" ht="125" customHeight="1" spans="1:8">
+      <c r="F16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:8">
       <c r="A17" s="4">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" ht="72" customHeight="1" spans="1:8">
+    </row>
+    <row r="18" customHeight="1" spans="1:8">
       <c r="A18" s="4">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" ht="72" customHeight="1" spans="1:8">
+      <c r="B18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:8">
       <c r="A19" s="4">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" ht="57" customHeight="1" spans="1:8">
+      <c r="B19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:8">
       <c r="A20" s="4">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" ht="74" customHeight="1" spans="1:8">
+      <c r="B20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:8">
       <c r="A21" s="4">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" ht="57" customHeight="1" spans="1:8">
-      <c r="A22" s="4">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" ht="29" spans="1:8">
-      <c r="A23" s="4">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>54</v>
+      <c r="F21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:H23" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <mergeCells count="9">
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="B4:B13"/>
-    <mergeCell ref="B14:B23"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-  </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.298611111111111" footer="0.298611111111111"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter/>
